--- a/Result/profitability/3158.xlsx
+++ b/Result/profitability/3158.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM42"/>
+  <dimension ref="A1:AM43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.73</v>
+        <v>1.7825</v>
       </c>
       <c r="N2" t="n">
-        <v>63.4025</v>
+        <v>63.99250000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8225</v>
+        <v>1.7725</v>
       </c>
       <c r="N3" t="n">
-        <v>63.9325</v>
+        <v>63.88125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6375</v>
+        <v>1.7025</v>
       </c>
       <c r="N4" t="n">
-        <v>62.425</v>
+        <v>62.5925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.17</v>
       </c>
       <c r="M5" t="n">
-        <v>1.60125</v>
+        <v>1.64125</v>
       </c>
       <c r="N5" t="n">
-        <v>61.70500000000001</v>
+        <v>61.59375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4575</v>
+        <v>1.50625</v>
       </c>
       <c r="N6" t="n">
-        <v>60.38250000000001</v>
+        <v>60.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.71</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4725</v>
+        <v>1.39</v>
       </c>
       <c r="N7" t="n">
-        <v>60.10125</v>
+        <v>60.36</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -5762,6 +5762,133 @@
       </c>
       <c r="AM42" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3158</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>295</v>
+      </c>
+      <c r="D43" t="n">
+        <v>102</v>
+      </c>
+      <c r="E43" t="n">
+        <v>193</v>
+      </c>
+      <c r="F43" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="G43" t="n">
+        <v>73</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>24.67%</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>75</v>
+      </c>
+      <c r="K43" t="n">
+        <v>60</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.84625</v>
+      </c>
+      <c r="N43" t="n">
+        <v>64.16625000000001</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.380000000000003</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.02158610980760201</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.1927710843373494</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>-0.8900000000000006</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>-0.01344410876132929</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
